--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484618_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484618_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6502</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7117</v>
+        <v>0.6502</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0257</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2806</v>
+        <v>0.6502</v>
       </c>
       <c r="H2" t="n">
-        <v>1.1686</v>
+        <v>0.6502</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9417</v>
+        <v>0.6502</v>
       </c>
       <c r="K2" t="n">
-        <v>1.4831</v>
+        <v>0.6502</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4586</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6611</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3145</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3466</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.4661</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8373</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5189</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3185</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>J. ROIG MESA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6502</v>
+        <v>0.2255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6502</v>
+        <v>-0.1557</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.3812</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6502</v>
+        <v>-0.8521</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6502</v>
+        <v>-0.3141</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.538</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6502</v>
+        <v>-0.1054</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6502</v>
+        <v>-0.1767</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.0712</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-0.7466</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.1374</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-0.6092</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.5724</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>0.5441</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.0283</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>E. DENIA VIVANCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.534</v>
+        <v>0.185</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8744</v>
+        <v>2.9814</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3405</v>
+        <v>-2.7964</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.9113</v>
+        <v>1.0675</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.7603</v>
+        <v>2.3533</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.151</v>
+        <v>-1.2858</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2869</v>
+        <v>3.9729</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.6045</v>
+        <v>2.5976</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3177</v>
+        <v>1.3753</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6244</v>
+        <v>-2.9054</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1558</v>
+        <v>-0.2443</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.4686</v>
+        <v>-2.6611</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.0995</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.8326</v>
+        <v>-2.7489</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8326</v>
+        <v>1.6493</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1233</v>
+        <v>0.2066</v>
       </c>
       <c r="T4" t="n">
-        <v>3.35</v>
+        <v>0.158</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2266</v>
+        <v>0.0486</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3219</v>
+        <v>0.0104</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6439</v>
+        <v>1.5993</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3219</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROIG MESA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4971</v>
+        <v>0.0347</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8287</v>
+        <v>1.1347</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3317</v>
+        <v>-1.1</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8521</v>
+        <v>1.2806</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3141</v>
+        <v>1.1686</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.538</v>
+        <v>0.112</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.1054</v>
+        <v>2.9417</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1767</v>
+        <v>1.4831</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0712</v>
+        <v>1.4586</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7466</v>
+        <v>-1.6611</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1374</v>
+        <v>-0.3145</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6092</v>
+        <v>-1.3466</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9163</v>
+        <v>-2.7489</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>1.2828</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1502</v>
+        <v>1.1861</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.129</v>
+        <v>0.9419</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0213</v>
+        <v>0.2441</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3219</v>
+        <v>-0.9658</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.9658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. DENIA VIVANCOS</t>
+          <t>E. CHOFRE TARREGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6801</v>
+        <v>-0.7993</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8686</v>
+        <v>0.2545</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5487</v>
+        <v>-1.0537</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0675</v>
+        <v>-1.6801</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3533</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2858</v>
+        <v>-0.9487</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9729</v>
+        <v>-0.477</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5976</v>
+        <v>-0.5543</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3753</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9054</v>
+        <v>-1.203</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2443</v>
+        <v>-0.1771</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.6611</v>
+        <v>-1.0259</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.0995</v>
+        <v>0.5498</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6493</v>
+        <v>0.5498</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6584</v>
+        <v>0.9749</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9547</v>
+        <v>0.7315</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2963</v>
+        <v>0.2434</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0104</v>
+        <v>-0.6439</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5993</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5889</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. CHOFRE TARREGA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2086</v>
+        <v>-1.2352</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1301</v>
+        <v>-0.2274</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0785</v>
+        <v>-1.0078</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6801</v>
+        <v>0.4209</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7314000000000001</v>
+        <v>1.3508</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9487</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.477</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5543</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07729999999999999</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.203</v>
+        <v>-0.3377</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1771</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0259</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5498</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5655</v>
+        <v>-0.2059</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3469</v>
+        <v>-0.0697</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2186</v>
+        <v>-0.1361</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6439</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6664</v>
+        <v>-1.7464</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.2821</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9582000000000001</v>
+        <v>-1.4643</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4209</v>
+        <v>-2.9113</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3508</v>
+        <v>-1.7603</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-1.151</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7586000000000001</v>
+        <v>-0.2869</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7586000000000001</v>
+        <v>-1.6045</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.3177</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3377</v>
+        <v>-2.6244</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5921999999999999</v>
+        <v>-0.1558</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-2.4686</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6371</v>
+        <v>0.8429</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5505</v>
+        <v>1.1935</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0866</v>
+        <v>-0.3505</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.267</v>
+        <v>0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.267</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.3577</v>
+        <v>-2.2374</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1041</v>
+        <v>-0.8168</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2536</v>
+        <v>-1.4206</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6385</v>
+        <v>-5.7397</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6127</v>
+        <v>1.1649</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0258</v>
+        <v>-6.9046</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-3.1717</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7714</v>
+        <v>1.2322</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7759</v>
+        <v>-4.4038</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.643</v>
+        <v>-2.568</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1587</v>
+        <v>-0.0673</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8017</v>
+        <v>-2.5008</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.5498</v>
+        <v>0.5498</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>0.464</v>
+        <v>-0.2149</v>
       </c>
       <c r="T9" t="n">
-        <v>0.402</v>
+        <v>0.1037</v>
       </c>
       <c r="U9" t="n">
-        <v>0.062</v>
+        <v>-0.3187</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6335</v>
+        <v>3.1674</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3219</v>
+        <v>3.1674</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. MARCO LOPEZ</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5238</v>
+        <v>-2.2397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2564</v>
+        <v>-1.9118</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.7803</v>
+        <v>-0.3279</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3712</v>
+        <v>-1.6385</v>
       </c>
       <c r="H10" t="n">
-        <v>2.6152</v>
+        <v>-1.6127</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.244</v>
+        <v>-0.0258</v>
       </c>
       <c r="J10" t="n">
-        <v>3.356</v>
+        <v>-0.9955000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5543</v>
+        <v>-1.7714</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8017</v>
+        <v>0.7759</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.9848</v>
+        <v>-0.643</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0609</v>
+        <v>0.1587</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.0457</v>
+        <v>-0.8017</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0158</v>
+        <v>-0.5498</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6493</v>
+        <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3878</v>
+        <v>0.582</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5656</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1778</v>
+        <v>-0.0123</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.267</v>
+        <v>-0.6335</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>H. MARCO LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1142</v>
+        <v>-2.4629</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.545</v>
+        <v>0.1192</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.5693</v>
+        <v>-2.5821</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.7397</v>
+        <v>0.3712</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1649</v>
+        <v>2.6152</v>
       </c>
       <c r="I11" t="n">
-        <v>-6.9046</v>
+        <v>-2.244</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.1717</v>
+        <v>3.356</v>
       </c>
       <c r="K11" t="n">
-        <v>1.2322</v>
+        <v>2.5543</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.4038</v>
+        <v>0.8017</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.568</v>
+        <v>-2.9848</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0673</v>
+        <v>0.0609</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.5008</v>
+        <v>-3.0457</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5498</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4661</v>
+        <v>1.6493</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0917</v>
+        <v>0.4487</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6244</v>
+        <v>0.4284</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4673</v>
+        <v>0.0203</v>
       </c>
       <c r="V11" t="n">
-        <v>3.1674</v>
+        <v>-1.267</v>
       </c>
       <c r="W11" t="n">
-        <v>3.1674</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1593</v>
+        <v>-4.4363</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7183</v>
+        <v>-2.144</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.441</v>
+        <v>-2.2923</v>
       </c>
       <c r="G12" t="n">
         <v>-3.5397</v>
@@ -1390,13 +1390,13 @@
         <v>2.1991</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1971</v>
+        <v>0.9201</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4638</v>
+        <v>1.0381</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2667</v>
+        <v>-0.118</v>
       </c>
       <c r="V12" t="n">
         <v>-1.267</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.337</v>
+        <v>-14.0618</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6730999999999996</v>
+        <v>-0.3978000000000004</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.6641</v>
+        <v>-13.6639</v>
       </c>
       <c r="G13" t="n">
         <v>-12.571</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9382</v>
+        <v>3.938200000000001</v>
       </c>
       <c r="I13" t="n">
         <v>-16.5092</v>
@@ -1447,7 +1447,7 @@
         <v>5.4042</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4836000000000005</v>
+        <v>0.4836</v>
       </c>
       <c r="M13" t="n">
         <v>-18.4585</v>
@@ -1468,10 +1468,10 @@
         <v>13.7443</v>
       </c>
       <c r="S13" t="n">
-        <v>5.0376</v>
+        <v>5.312899999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>5.3886</v>
+        <v>5.6638</v>
       </c>
       <c r="U13" t="n">
         <v>-0.3509</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.8361</v>
+        <v>5.1843</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4873</v>
+        <v>3.5835</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3488</v>
+        <v>1.6008</v>
       </c>
       <c r="G14" t="n">
         <v>3.8378</v>
@@ -1546,13 +1546,13 @@
         <v>2.3823</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1746</v>
+        <v>0.1736</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0347</v>
+        <v>0.1309</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2093</v>
+        <v>0.0428</v>
       </c>
       <c r="V14" t="n">
         <v>0.6231</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. GOMEZ CARBONELL</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.684</v>
+        <v>4.8233</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3394</v>
+        <v>5.3589</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3446</v>
+        <v>-0.5356</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7401</v>
+        <v>4.3501</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.033</v>
+        <v>-0.2818</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7731</v>
+        <v>4.6319</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7451</v>
+        <v>4.9719</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4834</v>
+        <v>0.1793</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2284</v>
+        <v>4.7925</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.005</v>
+        <v>-0.6217</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5496</v>
+        <v>-0.4611</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5446</v>
+        <v>-0.1606</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2828</v>
+        <v>3.1154</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.7325</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3273</v>
+        <v>-0.3639</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2448</v>
+        <v>-0.3686</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5785</v>
+        <v>0.8391</v>
       </c>
       <c r="W15" t="n">
-        <v>1.267</v>
+        <v>3.4998</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3115</v>
+        <v>-2.6606</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>J. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.28</v>
+        <v>4.7524</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8782</v>
+        <v>3.147</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5982</v>
+        <v>1.6054</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3501</v>
+        <v>1.7401</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2818</v>
+        <v>-1.033</v>
       </c>
       <c r="I16" t="n">
-        <v>4.6319</v>
+        <v>2.7731</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9719</v>
+        <v>1.7451</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1793</v>
+        <v>-0.4834</v>
       </c>
       <c r="L16" t="n">
-        <v>4.7925</v>
+        <v>2.2284</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6217</v>
+        <v>-0.005</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4611</v>
+        <v>-0.5496</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1606</v>
+        <v>0.5446</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.7489</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1154</v>
+        <v>1.2828</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2758</v>
+        <v>0.151</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8446</v>
+        <v>0.135</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4312</v>
+        <v>0.016</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8391</v>
+        <v>1.5785</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4998</v>
+        <v>1.267</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.6606</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8649</v>
+        <v>2.3137</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2917</v>
+        <v>-0.0994</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1567</v>
+        <v>2.4131</v>
       </c>
       <c r="G17" t="n">
         <v>0.5610000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.1991</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3296</v>
+        <v>0.1192</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2542</v>
+        <v>0.0022</v>
       </c>
       <c r="V17" t="n">
         <v>1.267</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.62</v>
+        <v>1.3652</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3638</v>
+        <v>1.4126</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2562</v>
+        <v>-0.0473</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7589</v>
+        <v>-0.2623</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6406</v>
+        <v>0.0198</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8817</v>
+        <v>-0.2822</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1466</v>
+        <v>0.2935</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0561</v>
+        <v>0.7678</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2027</v>
+        <v>-0.4743</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.9054</v>
+        <v>-0.5558</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5845</v>
+        <v>-0.748</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.321</v>
+        <v>0.1922</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3823</v>
+        <v>1.8326</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2986</v>
+        <v>1.8326</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4452</v>
+        <v>0.2332</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1335</v>
+        <v>0.1637</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6883</v>
+        <v>0.0696</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4486</v>
+        <v>-0.4382</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4486</v>
+        <v>-1.3937</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0345</v>
+        <v>1.139</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4126</v>
+        <v>1.7444</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3781</v>
+        <v>-0.6054</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2623</v>
+        <v>3.4933</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0198</v>
+        <v>1.2585</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2822</v>
+        <v>2.2348</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2935</v>
+        <v>3.938</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7678</v>
+        <v>1.1579</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4743</v>
+        <v>2.78</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5558</v>
+        <v>-0.4446</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.748</v>
+        <v>0.1006</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1922</v>
+        <v>-0.5452</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8326</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.7489</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0975</v>
+        <v>-0.76</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1637</v>
+        <v>-0.0886</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2612</v>
+        <v>-0.6714</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4382</v>
+        <v>-0.3115</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>0.6439</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3937</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.377</v>
+        <v>1.0329</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2637</v>
+        <v>0.5946</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8866000000000001</v>
+        <v>0.4383</v>
       </c>
       <c r="G20" t="n">
-        <v>3.4933</v>
+        <v>-0.7589</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2585</v>
+        <v>-2.6406</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2348</v>
+        <v>1.8817</v>
       </c>
       <c r="J20" t="n">
-        <v>3.938</v>
+        <v>1.1466</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1579</v>
+        <v>-1.0561</v>
       </c>
       <c r="L20" t="n">
-        <v>2.78</v>
+        <v>2.2027</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4446</v>
+        <v>-1.9054</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1006</v>
+        <v>-1.5845</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5452</v>
+        <v>-0.321</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.2828</v>
+        <v>2.3823</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.7489</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4661</v>
+        <v>3.2986</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.522</v>
+        <v>-0.142</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5694</v>
+        <v>0.3643</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9526</v>
+        <v>-0.5062</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3115</v>
+        <v>-0.4486</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.9554</v>
+        <v>-0.4486</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1538</v>
+        <v>0.2833</v>
       </c>
       <c r="E21" t="n">
-        <v>0.668</v>
+        <v>0.5718</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8218</v>
+        <v>-0.2886</v>
       </c>
       <c r="G21" t="n">
         <v>2.091</v>
@@ -2092,13 +2092,13 @@
         <v>1.2828</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2569</v>
+        <v>-0.8198</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0355</v>
+        <v>-0.0607</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2923</v>
+        <v>-0.7591</v>
       </c>
       <c r="V21" t="n">
         <v>-0.4382</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2057</v>
+        <v>-3.9929</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4571</v>
+        <v>-2.6494</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7486</v>
+        <v>-1.3435</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4813</v>
@@ -2170,13 +2170,13 @@
         <v>1.4661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9092</v>
+        <v>-0.6965</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1456</v>
+        <v>-0.0467</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0548</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-0.4486</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>14.337</v>
+        <v>16.9012</v>
       </c>
       <c r="E23" t="n">
-        <v>13.6642</v>
+        <v>13.664</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6729999999999998</v>
+        <v>3.2372</v>
       </c>
       <c r="G23" t="n">
         <v>12.5708</v>
@@ -2236,10 +2236,10 @@
         <v>-5.4044</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4834000000000003</v>
+        <v>-0.4834000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>4.5814</v>
+        <v>4.581399999999999</v>
       </c>
       <c r="Q23" t="n">
         <v>-13.7445</v>
@@ -2248,13 +2248,13 @@
         <v>18.3258</v>
       </c>
       <c r="S23" t="n">
-        <v>-5.037800000000001</v>
+        <v>-2.4738</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3508999999999998</v>
+        <v>0.3509</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.3887</v>
+        <v>-2.8244</v>
       </c>
       <c r="V23" t="n">
         <v>2.2226</v>
